--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487869_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487869_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. OKAFOR AUGUSTIN</t>
+          <t>J. REILLY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7987</v>
+        <v>2.4027</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5692</v>
+        <v>-0.5084</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2294</v>
+        <v>2.9111</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8745</v>
+        <v>2.251</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7592</v>
+        <v>2.1473</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1152</v>
+        <v>0.1037</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8459</v>
+        <v>1.3653</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7675</v>
+        <v>1.5882</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0784</v>
+        <v>-0.2229</v>
       </c>
       <c r="M2" t="n">
-        <v>1.0286</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0083</v>
+        <v>0.5591</v>
       </c>
       <c r="O2" t="n">
-        <v>1.0369</v>
+        <v>0.3266</v>
       </c>
       <c r="P2" t="n">
-        <v>1.2487</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2081</v>
+        <v>-2.0812</v>
       </c>
       <c r="R2" t="n">
         <v>1.4568</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3654</v>
+        <v>-0.1615</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.9601</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4339</v>
+        <v>0.7986</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.6899</v>
+        <v>0.9376</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6899</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. TSEGAKELE</t>
+          <t>M. OKAFOR AUGUSTIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2281</v>
+        <v>2.1352</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7201</v>
+        <v>0.1406</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9482</v>
+        <v>1.9945</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.2517</v>
+        <v>1.8745</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7953</v>
+        <v>0.7592</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4564</v>
+        <v>1.1152</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.2352</v>
+        <v>0.8459</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.5992</v>
+        <v>0.7675</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.636</v>
+        <v>0.0784</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0164</v>
+        <v>1.0286</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.196</v>
+        <v>-0.0083</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1796</v>
+        <v>1.0369</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6649</v>
+        <v>1.2487</v>
       </c>
       <c r="Q3" t="n">
+        <v>-0.2081</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.4568</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.2981</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.4972</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-0.6899</v>
+      </c>
+      <c r="W3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.6649</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.1696</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-0.6524</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.8221000000000001</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.6452</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.1675</v>
-      </c>
       <c r="X3" t="n">
-        <v>0.4776</v>
+        <v>-0.6899</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. REILLY</t>
+          <t>A. TSEGAKELE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7056</v>
+        <v>2.0585</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8532</v>
+        <v>-0.6549</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5588</v>
+        <v>2.7134</v>
       </c>
       <c r="G4" t="n">
-        <v>2.251</v>
+        <v>-1.2517</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1473</v>
+        <v>-0.7953</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1037</v>
+        <v>-0.4564</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3653</v>
+        <v>-1.2352</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5882</v>
+        <v>-0.5992</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2229</v>
+        <v>-0.636</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8856000000000001</v>
+        <v>-0.0164</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5591</v>
+        <v>-0.196</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3266</v>
+        <v>0.1796</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6244</v>
+        <v>1.6649</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8586</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3049</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4463</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9376</v>
+        <v>1.6452</v>
       </c>
       <c r="W4" t="n">
         <v>1.1675</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.23</v>
+        <v>0.4776</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4508</v>
+        <v>1.6922</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1558</v>
+        <v>-0.0906</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6066</v>
+        <v>1.7827</v>
       </c>
       <c r="G5" t="n">
         <v>1.4042</v>
@@ -844,13 +844,13 @@
         <v>1.0406</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2864</v>
+        <v>-0.045</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6524</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.366</v>
+        <v>0.5422</v>
       </c>
       <c r="V5" t="n">
         <v>-0.7076</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MENENDEZ GARCIA</t>
+          <t>T. PIERRE PHILIPPE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3099</v>
+        <v>1.4333</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.8207</v>
+        <v>-2.0981</v>
       </c>
       <c r="F6" t="n">
-        <v>4.1306</v>
+        <v>3.5314</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4408</v>
+        <v>2.414</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8998</v>
+        <v>1.2939</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3406</v>
+        <v>1.1201</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.0122</v>
+        <v>0.8794</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1689</v>
+        <v>1.6901</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1568</v>
+        <v>-0.8107</v>
       </c>
       <c r="M6" t="n">
-        <v>1.453</v>
+        <v>1.5347</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2692</v>
+        <v>-0.3962</v>
       </c>
       <c r="O6" t="n">
-        <v>1.1838</v>
+        <v>1.9309</v>
       </c>
       <c r="P6" t="n">
+        <v>-0.2081</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-2.2893</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-3.3299</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.0406</v>
+        <v>2.0812</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7609</v>
+        <v>-0.7726</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1239</v>
+        <v>-0.9182</v>
       </c>
       <c r="U6" t="n">
-        <v>1.637</v>
+        <v>0.1456</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.3975</v>
+        <v>0.23</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. PIERRE PHILIPPE</t>
+          <t>J. MENENDEZ GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9651</v>
+        <v>0.0276</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4196</v>
+        <v>-3.3984</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3846</v>
+        <v>3.426</v>
       </c>
       <c r="G7" t="n">
-        <v>2.414</v>
+        <v>0.4408</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2939</v>
+        <v>-0.8998</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1201</v>
+        <v>1.3406</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8794</v>
+        <v>-1.0122</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6901</v>
+        <v>-1.1689</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8107</v>
+        <v>0.1568</v>
       </c>
       <c r="M7" t="n">
-        <v>1.5347</v>
+        <v>1.453</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3962</v>
+        <v>0.2692</v>
       </c>
       <c r="O7" t="n">
-        <v>1.9309</v>
+        <v>1.1838</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2081</v>
+        <v>-2.2893</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2893</v>
+        <v>-3.3299</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0812</v>
+        <v>1.0406</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2409</v>
+        <v>0.4786</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2396</v>
+        <v>-0.4538</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0012</v>
+        <v>0.9324</v>
       </c>
       <c r="V7" t="n">
+        <v>1.3975</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.3975</v>
+      </c>
+      <c r="X7" t="n">
         <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. DUKE TOUSSAINT</t>
+          <t>S. FRANCO GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6102</v>
+        <v>-0.5188</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.399</v>
+        <v>-0.8406</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7889</v>
+        <v>0.3218</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2338</v>
+        <v>-0.6912</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7014</v>
+        <v>-0.9957</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5324</v>
+        <v>0.3045</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8258</v>
+        <v>-0.2829</v>
       </c>
       <c r="K8" t="n">
-        <v>0.62</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2058</v>
+        <v>0.3739</v>
       </c>
       <c r="M8" t="n">
-        <v>0.408</v>
+        <v>-0.4083</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0814</v>
+        <v>-0.3389</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3266</v>
+        <v>-0.0694</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.9137</v>
+        <v>0.6244</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.1624</v>
+        <v>-0.2081</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4234</v>
+        <v>-0.452</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.46</v>
+        <v>-0.3495</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8834</v>
+        <v>-0.1024</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3538</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7513</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. FRANCO GARCIA</t>
+          <t>I. DUKE TOUSSAINT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6912</v>
+        <v>-0.6647</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.013</v>
+        <v>-1.4829</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3218</v>
+        <v>0.8182</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6912</v>
+        <v>2.2338</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9957</v>
+        <v>0.7014</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3045</v>
+        <v>1.5324</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2829</v>
+        <v>1.8258</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6568000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3739</v>
+        <v>1.2058</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4083</v>
+        <v>0.408</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3389</v>
+        <v>0.0814</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0694</v>
+        <v>0.3266</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6244</v>
+        <v>-2.9137</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2081</v>
+        <v>-4.1624</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6244</v>
+        <v>0.369</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5219</v>
+        <v>-0.5438</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1024</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.3538</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3929</v>
+        <v>-0.8529</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5663</v>
+        <v>-3.1143</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1734</v>
+        <v>2.2615</v>
       </c>
       <c r="G10" t="n">
         <v>1.1453</v>
@@ -1234,13 +1234,13 @@
         <v>2.4974</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4351</v>
+        <v>0.1049</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.4354</v>
+        <v>-0.9834000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0002</v>
+        <v>1.0883</v>
       </c>
       <c r="V10" t="n">
         <v>-0.23</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1379</v>
+        <v>-1.4347</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2897</v>
+        <v>-2.9682</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1518</v>
+        <v>1.5335</v>
       </c>
       <c r="G11" t="n">
         <v>2.3444</v>
@@ -1312,13 +1312,13 @@
         <v>0.2081</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2148</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7177</v>
+        <v>-0.3962</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4971</v>
+        <v>-0.1154</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3538</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.625999999999999</v>
+        <v>6.2784</v>
       </c>
       <c r="E12" t="n">
-        <v>-15.6682</v>
+        <v>-15.0158</v>
       </c>
       <c r="F12" t="n">
         <v>21.2941</v>
@@ -1369,7 +1369,7 @@
         <v>4.6557</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3265</v>
+        <v>0.3264999999999998</v>
       </c>
       <c r="M12" t="n">
         <v>7.1829</v>
@@ -1390,13 +1390,13 @@
         <v>13.5276</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9409</v>
+        <v>-1.2883</v>
       </c>
       <c r="T12" t="n">
-        <v>-6.9289</v>
+        <v>-6.2766</v>
       </c>
       <c r="U12" t="n">
-        <v>4.988199999999999</v>
+        <v>4.9883</v>
       </c>
       <c r="V12" t="n">
         <v>1.6452</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. BADJI</t>
+          <t>I. AIZPITARTE ARANZA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.727</v>
+        <v>2.609</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.585</v>
+        <v>0.0313</v>
       </c>
       <c r="F13" t="n">
-        <v>3.312</v>
+        <v>2.5777</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.9453</v>
+        <v>-0.0497</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.1453</v>
+        <v>0.1895</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2</v>
+        <v>-0.2392</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9818</v>
+        <v>-0.0985</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1778</v>
+        <v>0.251</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1959</v>
+        <v>-0.3495</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0365</v>
+        <v>0.0488</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0324</v>
+        <v>-0.0614</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0041</v>
+        <v>0.1102</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8731</v>
+        <v>1.4568</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R13" t="n">
-        <v>2.9137</v>
+        <v>2.4974</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.3882</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7738</v>
+        <v>-0.2271</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5293</v>
+        <v>0.6153</v>
       </c>
       <c r="V13" t="n">
-        <v>1.0437</v>
+        <v>0.8137</v>
       </c>
       <c r="W13" t="n">
-        <v>2.2112</v>
+        <v>1.3975</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1675</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. AIZPITARTE ARANZA</t>
+          <t>P. BADJI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6853</v>
+        <v>2.3644</v>
       </c>
       <c r="E14" t="n">
-        <v>0.46</v>
+        <v>-0.4779</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2254</v>
+        <v>2.8422</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0497</v>
+        <v>-0.9453</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1895</v>
+        <v>-1.1453</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2392</v>
+        <v>0.2</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0985</v>
+        <v>-0.9818</v>
       </c>
       <c r="K14" t="n">
-        <v>0.251</v>
+        <v>-1.1778</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.3495</v>
+        <v>0.1959</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0488</v>
+        <v>0.0365</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0614</v>
+        <v>0.0324</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1102</v>
+        <v>0.0041</v>
       </c>
       <c r="P14" t="n">
-        <v>1.4568</v>
+        <v>1.8731</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4974</v>
+        <v>2.9137</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4645</v>
+        <v>0.3929</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2015</v>
+        <v>-0.6667</v>
       </c>
       <c r="U14" t="n">
-        <v>0.263</v>
+        <v>1.0596</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8137</v>
+        <v>1.0437</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3975</v>
+        <v>2.2112</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5838</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0488</v>
+        <v>2.0283</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.0113</v>
+        <v>-0.797</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0601</v>
+        <v>2.8252</v>
       </c>
       <c r="G15" t="n">
         <v>-0.323</v>
@@ -1624,13 +1624,13 @@
         <v>2.0812</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5206</v>
+        <v>0.5001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4476</v>
+        <v>-0.2333</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>-0.23</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7496</v>
+        <v>0.4678</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4646</v>
+        <v>0.036</v>
       </c>
       <c r="F16" t="n">
-        <v>0.285</v>
+        <v>0.4318</v>
       </c>
       <c r="G16" t="n">
         <v>-1.3145</v>
@@ -1702,13 +1702,13 @@
         <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3555</v>
+        <v>0.0737</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1924</v>
+        <v>-0.2362</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1631</v>
+        <v>0.3099</v>
       </c>
       <c r="V16" t="n">
         <v>0.4599</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9674</v>
+        <v>-0.8911</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.745</v>
+        <v>-1.3163</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7776</v>
+        <v>0.4252</v>
       </c>
       <c r="G17" t="n">
         <v>-0.857</v>
@@ -1780,13 +1780,13 @@
         <v>1.6649</v>
       </c>
       <c r="S17" t="n">
-        <v>0.079</v>
+        <v>0.1553</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2396</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3186</v>
+        <v>0.9663</v>
       </c>
       <c r="V17" t="n">
         <v>-0.8137</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2423</v>
+        <v>-1.417</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.752</v>
+        <v>-1.0735</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4903</v>
+        <v>-0.3435</v>
       </c>
       <c r="G18" t="n">
         <v>0.6879</v>
@@ -1858,13 +1858,13 @@
         <v>0.8325</v>
       </c>
       <c r="S18" t="n">
-        <v>0.486</v>
+        <v>0.3114</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3882</v>
+        <v>0.0667</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0979</v>
+        <v>0.2447</v>
       </c>
       <c r="V18" t="n">
         <v>-1.1675</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4513</v>
+        <v>-1.8036</v>
       </c>
       <c r="E19" t="n">
         <v>-2.137</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6857</v>
+        <v>0.3334</v>
       </c>
       <c r="G19" t="n">
         <v>-2.8442</v>
@@ -1936,13 +1936,13 @@
         <v>1.0406</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3523</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>-0.7177</v>
       </c>
       <c r="U19" t="n">
-        <v>1.07</v>
+        <v>0.7177</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MONCANUT MORE</t>
+          <t>N. WILLIAMS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0774</v>
+        <v>-2.6476</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.2333</v>
+        <v>-3.6443</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1559</v>
+        <v>0.9967</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0951</v>
+        <v>-2.3178</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0682</v>
+        <v>-0.6335</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1633</v>
+        <v>-1.6843</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0603</v>
+        <v>-1.746</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3705</v>
+        <v>-0.0944</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3103</v>
+        <v>-1.6516</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1554</v>
+        <v>-0.5717</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3023</v>
+        <v>-0.5391</v>
       </c>
       <c r="O20" t="n">
-        <v>0.147</v>
+        <v>-0.0326</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.538</v>
+        <v>1.2487</v>
       </c>
       <c r="Q20" t="n">
-        <v>-6.2435</v>
+        <v>-1.0406</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7055</v>
+        <v>2.2893</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4318</v>
+        <v>-0.1811</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1363</v>
+        <v>-0.8577</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2956</v>
+        <v>0.6766</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1238</v>
+        <v>-1.3975</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6899</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. WILLIAMS</t>
+          <t>M. NIANG NDONGO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4374</v>
+        <v>-3.1148</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.2872</v>
+        <v>-6.0393</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8499</v>
+        <v>2.9244</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.3178</v>
+        <v>-4.1064</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6335</v>
+        <v>-3.4222</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6843</v>
+        <v>-0.6842</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.746</v>
+        <v>-3.7224</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0944</v>
+        <v>-2.7852</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.6516</v>
+        <v>-0.9373</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5717</v>
+        <v>-0.384</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5391</v>
+        <v>-0.6371</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0326</v>
+        <v>0.2531</v>
       </c>
       <c r="P21" t="n">
-        <v>1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2893</v>
+        <v>2.4974</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9708</v>
+        <v>0.0124</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.5006</v>
+        <v>-0.7986</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5298</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.3975</v>
+        <v>-0.4776</v>
       </c>
       <c r="W21" t="n">
+        <v>-0.4776</v>
+      </c>
+      <c r="X21" t="n">
         <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-1.3975</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. NIANG NDONGO</t>
+          <t>A. MONCANUT MORE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6609</v>
+        <v>-3.2212</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.4679</v>
+        <v>-5.8762</v>
       </c>
       <c r="F22" t="n">
-        <v>2.807</v>
+        <v>2.655</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.1064</v>
+        <v>-0.0951</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.4222</v>
+        <v>0.0682</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6842</v>
+        <v>-0.1633</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.7224</v>
+        <v>0.0603</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.7852</v>
+        <v>0.3705</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.9373</v>
+        <v>-0.3103</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.384</v>
+        <v>-0.1554</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6371</v>
+        <v>-0.3023</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2531</v>
+        <v>0.147</v>
       </c>
       <c r="P22" t="n">
-        <v>1.4568</v>
+        <v>-3.538</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0406</v>
+        <v>-6.2435</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4974</v>
+        <v>2.7055</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5337</v>
+        <v>0.288</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2272</v>
+        <v>-0.5067</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6936</v>
+        <v>0.7947</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.4776</v>
+        <v>0.1238</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.4776</v>
+        <v>0.8137</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6899</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.625999999999999</v>
+        <v>-5.6258</v>
       </c>
       <c r="E23" t="n">
-        <v>-21.2941</v>
+        <v>-21.2942</v>
       </c>
       <c r="F23" t="n">
-        <v>15.6683</v>
+        <v>15.6681</v>
       </c>
       <c r="G23" t="n">
         <v>-12.1651</v>
@@ -2218,28 +2218,28 @@
         <v>-5.0214</v>
       </c>
       <c r="I23" t="n">
-        <v>-7.1438</v>
+        <v>-7.143800000000001</v>
       </c>
       <c r="J23" t="n">
         <v>-7.183</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3657999999999997</v>
+        <v>-0.3658</v>
       </c>
       <c r="L23" t="n">
         <v>-6.817299999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.9821</v>
+        <v>-4.982100000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-4.655600000000001</v>
+        <v>-4.6556</v>
       </c>
       <c r="O23" t="n">
         <v>-0.3264</v>
       </c>
       <c r="P23" t="n">
-        <v>6.243600000000002</v>
+        <v>6.243599999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-13.5277</v>
@@ -2248,13 +2248,13 @@
         <v>19.7712</v>
       </c>
       <c r="S23" t="n">
-        <v>1.9407</v>
+        <v>1.9409</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.9881</v>
+        <v>-4.988300000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>6.9291</v>
+        <v>6.9292</v>
       </c>
       <c r="V23" t="n">
         <v>-1.6452</v>
@@ -2263,7 +2263,7 @@
         <v>4.4047</v>
       </c>
       <c r="X23" t="n">
-        <v>-6.0499</v>
+        <v>-6.049899999999999</v>
       </c>
     </row>
   </sheetData>
